--- a/currentbuild/StructureDefinition-demo-at-patient.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,13 +66,13 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Norge</t>
+    <t>Helsedirektoratet</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Norge (https://www.hl7.no)</t>
+    <t>Helsedirektoratet (https://www.helsedirektoratet.no)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/currentbuild/StructureDefinition-demo-at-patient.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-demo-at-patient.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-demo-at-patient.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -472,25 +472,29 @@
     <t>The registered place of birth of the patient. A sytem may use the address.text if they don't store the birthPlace address in discrete elements.</t>
   </si>
   <si>
-    <t>Patient.extension:birthPlace.id</t>
-  </si>
-  <si>
-    <t>Patient.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Patient.extension:birthPlace.id</t>
+  </si>
+  <si>
+    <t>Patient.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -540,14 +544,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Patient.extension:sex-for-clinical-use</t>
@@ -563,7 +563,7 @@
     <t>Sex for clinical use</t>
   </si>
   <si>
-    <t>A parameter that provides guidance on how a recipient should apply settings or reference ranges that are derived from observable information such as an organ inventory, recent hormone lab tests, genetic testing, menstrual status, obstetric history, etc..</t>
+    <t>A parameter that provides guidance on how a recipient should apply settings or reference ranges that are derived from observable information such as an organ inventory, recent hormone lab tests, genetic testing, menstrual status, obstetric history, etc.</t>
   </si>
   <si>
     <t>Patient.extension:gender-identity</t>
@@ -768,10 +768,6 @@
   </si>
   <si>
     <t>Patient.name.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Patient.name.extension</t>
@@ -3045,7 +3041,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -3068,10 +3064,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3094,13 +3090,13 @@
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3151,7 +3147,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3160,13 +3156,13 @@
         <v>89</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>81</v>
@@ -3183,10 +3179,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3257,7 +3253,7 @@
         <v>137</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>81</v>
@@ -3266,7 +3262,7 @@
         <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3298,10 +3294,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3327,13 +3323,13 @@
         <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3341,7 +3337,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>81</v>
@@ -3383,7 +3379,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3415,10 +3411,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3441,13 +3437,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3498,7 +3494,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3507,7 +3503,7 @@
         <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
@@ -3624,7 +3620,7 @@
         <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>140</v>
@@ -3743,7 +3739,7 @@
         <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>140</v>
@@ -3860,7 +3856,7 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>140</v>
@@ -3977,7 +3973,7 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>140</v>
@@ -4094,7 +4090,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>140</v>
@@ -4213,7 +4209,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>140</v>
@@ -4579,7 +4575,7 @@
         <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>227</v>
@@ -4738,13 +4734,13 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4795,7 +4791,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4810,7 +4806,7 @@
         <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
@@ -4827,10 +4823,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4856,10 +4852,10 @@
         <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>207</v>
@@ -4903,7 +4899,7 @@
         <v>137</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>81</v>
@@ -4912,7 +4908,7 @@
         <v>138</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4927,7 +4923,7 @@
         <v>140</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
@@ -4944,10 +4940,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4973,16 +4969,16 @@
         <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5007,31 +5003,31 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5046,16 +5042,16 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5063,10 +5059,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5089,19 +5085,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5150,7 +5146,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5165,16 +5161,16 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5182,14 +5178,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5208,16 +5204,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5231,43 +5227,43 @@
         <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5282,16 +5278,16 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5299,14 +5295,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5325,16 +5321,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5384,7 +5380,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5399,16 +5395,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5416,10 +5412,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5442,13 +5438,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5499,7 +5495,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5514,16 +5510,16 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5531,10 +5527,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5557,13 +5553,13 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5614,7 +5610,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5629,16 +5625,16 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5646,10 +5642,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5672,17 +5668,17 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5731,7 +5727,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5746,16 +5742,16 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -5763,10 +5759,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5789,19 +5785,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5850,7 +5846,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5865,16 +5861,16 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -5882,10 +5878,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5911,16 +5907,16 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5945,14 +5941,14 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5969,7 +5965,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5984,16 +5980,16 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6001,10 +5997,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6027,19 +6023,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6088,7 +6084,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6103,27 +6099,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6146,19 +6142,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6207,7 +6203,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6222,16 +6218,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6239,10 +6235,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6265,19 +6261,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6326,7 +6322,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6341,16 +6337,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6358,10 +6354,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6384,17 +6380,17 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6419,14 +6415,14 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6443,7 +6439,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6458,16 +6454,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6475,10 +6471,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6501,19 +6497,19 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6562,7 +6558,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6577,16 +6573,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6594,10 +6590,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6620,19 +6616,19 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6681,7 +6677,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6696,16 +6692,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6713,10 +6709,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6739,19 +6735,19 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6800,7 +6796,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6812,13 +6808,13 @@
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AK42" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AL42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
@@ -6832,10 +6828,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6858,13 +6854,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6915,7 +6911,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6930,7 +6926,7 @@
         <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
@@ -6947,10 +6943,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6976,10 +6972,10 @@
         <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>207</v>
@@ -7032,7 +7028,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7047,7 +7043,7 @@
         <v>140</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -7064,14 +7060,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7093,10 +7089,10 @@
         <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>207</v>
@@ -7151,7 +7147,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7183,10 +7179,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7209,17 +7205,17 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7244,14 +7240,14 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7268,7 +7264,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7283,16 +7279,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7300,10 +7296,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7329,14 +7325,14 @@
         <v>229</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7385,7 +7381,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7403,13 +7399,13 @@
         <v>235</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7417,10 +7413,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7443,19 +7439,19 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7504,7 +7500,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7519,16 +7515,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7536,10 +7532,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7562,17 +7558,17 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7621,7 +7617,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7636,16 +7632,16 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7653,10 +7649,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7682,14 +7678,14 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -7714,14 +7710,14 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7738,7 +7734,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7753,16 +7749,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -7770,10 +7766,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7796,17 +7792,17 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -7855,7 +7851,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7864,22 +7860,22 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -7887,10 +7883,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7913,13 +7909,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7970,7 +7966,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7985,10 +7981,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -8002,10 +7998,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8028,19 +8024,19 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8089,7 +8085,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8104,10 +8100,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -8121,10 +8117,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8147,13 +8143,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8204,7 +8200,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8219,7 +8215,7 @@
         <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8236,10 +8232,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8265,10 +8261,10 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>207</v>
@@ -8321,7 +8317,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8336,7 +8332,7 @@
         <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -8353,14 +8349,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8382,10 +8378,10 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>207</v>
@@ -8440,7 +8436,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8472,10 +8468,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8498,19 +8494,19 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8559,7 +8555,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8574,16 +8570,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8591,10 +8587,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8620,16 +8616,16 @@
         <v>220</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8678,7 +8674,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8693,16 +8689,16 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8710,14 +8706,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8736,16 +8732,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8795,7 +8791,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8810,16 +8806,16 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -8827,10 +8823,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8853,19 +8849,19 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8914,7 +8910,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8929,10 +8925,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -8946,10 +8942,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8972,19 +8968,19 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9033,7 +9029,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9048,10 +9044,10 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
@@ -9065,10 +9061,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9091,13 +9087,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9148,7 +9144,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9163,7 +9159,7 @@
         <v>81</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
@@ -9180,10 +9176,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9209,10 +9205,10 @@
         <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>207</v>
@@ -9265,7 +9261,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9280,7 +9276,7 @@
         <v>140</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
@@ -9297,14 +9293,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9326,10 +9322,10 @@
         <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>207</v>
@@ -9384,7 +9380,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9416,10 +9412,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9442,16 +9438,16 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9501,7 +9497,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>89</v>
@@ -9519,13 +9515,13 @@
         <v>215</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9533,10 +9529,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9562,10 +9558,10 @@
         <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9592,14 +9588,14 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9616,7 +9612,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>89</v>
@@ -9631,10 +9627,10 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>

--- a/currentbuild/StructureDefinition-demo-at-patient.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-demo-at-patient.xlsx
+++ b/currentbuild/StructureDefinition-demo-at-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
